--- a/public/planilhas/05_motor_precificacao.xlsx
+++ b/public/planilhas/05_motor_precificacao.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PONTO_EQUILIBRIO" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,13 +20,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;—&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,6 +145,37 @@
       <color rgb="00F3ECDD"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00C99C66"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -193,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -241,7 +274,22 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="17" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="24" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -251,12 +299,29 @@
     <xf numFmtId="166" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="0043D07F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="00D9534F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -414,6 +479,219 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cascata · custo → preço</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$20:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$20:$C$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!D19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E9E5B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$20:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$D$20:$D$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!E19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D9534F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$20:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$E$20:$E$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!O19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15000">
+              <a:solidFill>
+                <a:srgbClr val="C99C66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$N$20:$N$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$O$20:$O$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
@@ -552,6 +830,50 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3600000" cy="1440000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -876,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -998,22 +1320,22 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="7">
-        <f>B40</f>
+        <f>Z40</f>
         <v/>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="8">
-        <f>B41</f>
+        <f>Z41</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="9">
-        <f>B42</f>
+        <f>Z42</f>
         <v/>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="10">
-        <f>B43</f>
+        <f>Z43</f>
         <v/>
       </c>
       <c r="I6" s="6" t="n"/>
@@ -1115,7 +1437,7 @@
         <v>0.15</v>
       </c>
       <c r="D11" s="17">
-        <f>$B$44/(1-C11)</f>
+        <f>$Z$44/(1-C11)</f>
         <v/>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -1142,7 +1464,7 @@
         <v>0.3</v>
       </c>
       <c r="D12" s="17">
-        <f>$B$44/(1-C12)</f>
+        <f>$Z$44/(1-C12)</f>
         <v/>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -1169,7 +1491,7 @@
         <v>0.5</v>
       </c>
       <c r="D13" s="17">
-        <f>$B$44/(1-C13)</f>
+        <f>$Z$44/(1-C13)</f>
         <v/>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -1246,7 +1568,11 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Cascata do preço ideal</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -1257,62 +1583,200 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
-    </row>
-    <row r="19">
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>Spark · preço × margem</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>Ponto</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="P19" s="22" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Custo entrega</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="24">
+        <f>IF(G20&gt;=0,G20,0)</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>IF(G20&lt;0,-G20,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>G20</f>
+        <v/>
+      </c>
+      <c r="G20" s="25">
+        <f>$Z$44</f>
+        <v/>
+      </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
+      <c r="N20" s="26" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="O20" s="27">
+        <f>$Z$44/(1-0.10)</f>
+        <v/>
+      </c>
+      <c r="P20" s="28">
+        <f>IF(OR(O20="",NOT(ISNUMBER(O20))),"",REPT("▬",MAX(1,ROUND((O20-(MIN(O20:O24)))/MAX(1E-9,(MAX(O20:O24))-(MIN(O20:O24)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>+ Margem ideal 30%</t>
+        </is>
+      </c>
+      <c r="C21" s="24">
+        <f>IF(G21&gt;=0,F20,F20+G21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>IF(G21&gt;=0,G21,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>IF(G21&lt;0,-G21,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>F20+G21</f>
+        <v/>
+      </c>
+      <c r="G21" s="25">
+        <f>$D$12-$Z$44</f>
+        <v/>
+      </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
+      <c r="N21" s="26" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="O21" s="27">
+        <f>$Z$44/(1-0.20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="28">
+        <f>IF(OR(O21="",NOT(ISNUMBER(O21))),"",REPT("▬",MAX(1,ROUND((O21-(MIN(O20:O24)))/MAX(1E-9,(MAX(O20:O24))-(MIN(O20:O24)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Preço ideal</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="24">
+        <f>IF(G22&gt;=0,G22,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>IF(G22&lt;0,-G22,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="G22" s="25">
+        <f>$D$12</f>
+        <v/>
+      </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
+      <c r="N22" s="26" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="O22" s="27">
+        <f>$Z$44/(1-0.30)</f>
+        <v/>
+      </c>
+      <c r="P22" s="28">
+        <f>IF(OR(O22="",NOT(ISNUMBER(O22))),"",REPT("▬",MAX(1,ROUND((O22-(MIN(O20:O24)))/MAX(1E-9,(MAX(O20:O24))-(MIN(O20:O24)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1327,6 +1791,19 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
+      <c r="N23" s="26" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="O23" s="27">
+        <f>$Z$44/(1-0.40)</f>
+        <v/>
+      </c>
+      <c r="P23" s="28">
+        <f>IF(OR(O23="",NOT(ISNUMBER(O23))),"",REPT("▬",MAX(1,ROUND((O23-(MIN(O20:O24)))/MAX(1E-9,(MAX(O20:O24))-(MIN(O20:O24)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1341,6 +1818,19 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
+      <c r="N24" s="26" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="O24" s="27">
+        <f>$Z$44/(1-0.50)</f>
+        <v/>
+      </c>
+      <c r="P24" s="28">
+        <f>IF(OR(O24="",NOT(ISNUMBER(O24))),"",REPT("▬",MAX(1,ROUND((O24-(MIN(O20:O24)))/MAX(1E-9,(MAX(O20:O24))-(MIN(O20:O24)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1386,7 +1876,11 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>MINI-SPARKLINES</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
@@ -1398,59 +1892,164 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Atual</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Valor/hora</t>
+        </is>
+      </c>
+      <c r="C30" s="29">
+        <f>$Z$40</f>
+        <v/>
+      </c>
+      <c r="D30" s="30" t="n">
+        <v>180</v>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>190</v>
+      </c>
+      <c r="F30" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="G30" s="30" t="n">
+        <v>210</v>
+      </c>
+      <c r="H30" s="30" t="n">
+        <v>220</v>
+      </c>
+      <c r="I30" s="30">
+        <f>$Z$40</f>
+        <v/>
+      </c>
+      <c r="J30" s="31">
+        <f>IF(D30=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D30-(MIN(D30:I30)))/MAX(1E-9,(MAX(D30:I30))-(MIN(D30:I30)))*7+1,0))),1))&amp;IF(E30=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E30-(MIN(D30:I30)))/MAX(1E-9,(MAX(D30:I30))-(MIN(D30:I30)))*7+1,0))),1))&amp;IF(F30=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F30-(MIN(D30:I30)))/MAX(1E-9,(MAX(D30:I30))-(MIN(D30:I30)))*7+1,0))),1))&amp;IF(G30=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G30-(MIN(D30:I30)))/MAX(1E-9,(MAX(D30:I30))-(MIN(D30:I30)))*7+1,0))),1))&amp;IF(H30=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H30-(MIN(D30:I30)))/MAX(1E-9,(MAX(D30:I30))-(MIN(D30:I30)))*7+1,0))),1))&amp;IF(I30=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I30-(MIN(D30:I30)))/MAX(1E-9,(MAX(D30:I30))-(MIN(D30:I30)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Break-even un.</t>
+        </is>
+      </c>
+      <c r="C31" s="29">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>75</v>
+      </c>
+      <c r="F31" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="H31" s="30" t="n">
+        <v>62</v>
+      </c>
+      <c r="I31" s="30">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="J31" s="31">
+        <f>IF(D31=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D31-(MIN(D31:I31)))/MAX(1E-9,(MAX(D31:I31))-(MIN(D31:I31)))*7+1,0))),1))&amp;IF(E31=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E31-(MIN(D31:I31)))/MAX(1E-9,(MAX(D31:I31))-(MIN(D31:I31)))*7+1,0))),1))&amp;IF(F31=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F31-(MIN(D31:I31)))/MAX(1E-9,(MAX(D31:I31))-(MIN(D31:I31)))*7+1,0))),1))&amp;IF(G31=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G31-(MIN(D31:I31)))/MAX(1E-9,(MAX(D31:I31))-(MIN(D31:I31)))*7+1,0))),1))&amp;IF(H31=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H31-(MIN(D31:I31)))/MAX(1E-9,(MAX(D31:I31))-(MIN(D31:I31)))*7+1,0))),1))&amp;IF(I31=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I31-(MIN(D31:I31)))/MAX(1E-9,(MAX(D31:I31))-(MIN(D31:I31)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Margem %</t>
+        </is>
+      </c>
+      <c r="C32" s="29">
+        <f>$Z$43*100</f>
+        <v/>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="I32" s="30">
+        <f>$Z$43*100</f>
+        <v/>
+      </c>
+      <c r="J32" s="31">
+        <f>IF(D32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(E32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(F32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(G32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(H32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(I32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
     </row>
@@ -1554,10 +2153,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="21">
-        <f>ENTRADAS!B11</f>
-        <v/>
-      </c>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -1568,13 +2164,14 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
+      <c r="Z40" s="32">
+        <f>ENTRADAS!B11</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="21">
-        <f>IFERROR(ENTRADAS!B6/ENTRADAS!B12,0)</f>
-        <v/>
-      </c>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
@@ -1585,13 +2182,14 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
+      <c r="Z41" s="32">
+        <f>IFERROR(ENTRADAS!B6/ENTRADAS!B12,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="21">
-        <f>B41*ENTRADAS!B9</f>
-        <v/>
-      </c>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -1602,13 +2200,14 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
+      <c r="Z42" s="32">
+        <f>Z41*ENTRADAS!B9</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="21">
-        <f>ENTRADAS!B13</f>
-        <v/>
-      </c>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
@@ -1619,13 +2218,14 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
+      <c r="Z43" s="32">
+        <f>ENTRADAS!B13</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="21">
-        <f>(ENTRADAS!B7*ENTRADAS!B11)+ENTRADAS!E7</f>
-        <v/>
-      </c>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -1636,6 +2236,10 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
+      <c r="Z44" s="32">
+        <f>(ENTRADAS!B7*ENTRADAS!B11)+ENTRADAS!E7</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1813,6 +2417,23 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="H5:I5"/>
   </mergeCells>
+  <conditionalFormatting sqref="G20:G22">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C30:C32">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00C99C66"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1888,21 +2509,21 @@
       <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Renda desejada / mês</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="34" t="n">
         <v>20000</v>
       </c>
       <c r="C5" s="2" t="n"/>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>Nome do serviço/produto</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Plano Pro</t>
         </is>
@@ -1912,21 +2533,21 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Custos fixos / mês</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="34" t="n">
         <v>7000</v>
       </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Horas por entrega</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="36" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="n"/>
@@ -1934,21 +2555,21 @@
       <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Horas produtivas / mês</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="37" t="n">
         <v>120</v>
       </c>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>Custos extras / entrega</t>
         </is>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="34" t="n">
         <v>120</v>
       </c>
       <c r="F7" s="2" t="n"/>
@@ -1956,21 +2577,21 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Custo variável / unidade</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="34" t="n">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>Preço-alvo do cliente</t>
         </is>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="34" t="n">
         <v>1200</v>
       </c>
       <c r="F8" s="2" t="n"/>
@@ -1978,12 +2599,12 @@
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Preço de venda / unidade</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="34" t="n">
         <v>149</v>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -2004,12 +2625,12 @@
       <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>VALOR DA HORA</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="39">
         <f>(B5+B6)/B7</f>
         <v/>
       </c>
@@ -2021,12 +2642,12 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>MARGEM DE CONTRIB./UNID.</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="40">
         <f>IFERROR(B9-B8,0)</f>
         <v/>
       </c>
@@ -2038,12 +2659,12 @@
       <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>% MARGEM DE CONTRIBUIÇÃO</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="41">
         <f>IFERROR(B12/B9,0)</f>
         <v/>
       </c>
@@ -2428,18 +3049,18 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="n">
+      <c r="A6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="42">
         <f>A6*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="42">
         <f>ENTRADAS!$B$6+A6*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="42">
         <f>B6-C6</f>
         <v/>
       </c>
@@ -2449,18 +3070,18 @@
       <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="n">
+      <c r="A7" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="42">
         <f>A7*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="42">
         <f>ENTRADAS!$B$6+A7*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="42">
         <f>B7-C7</f>
         <v/>
       </c>
@@ -2470,18 +3091,18 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="42">
         <f>A8*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="42">
         <f>ENTRADAS!$B$6+A8*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="42">
         <f>B8-C8</f>
         <v/>
       </c>
@@ -2491,18 +3112,18 @@
       <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="n">
+      <c r="A9" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="42">
         <f>A9*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="42">
         <f>ENTRADAS!$B$6+A9*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="42">
         <f>B9-C9</f>
         <v/>
       </c>
@@ -2512,18 +3133,18 @@
       <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="n">
+      <c r="A10" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="42">
         <f>A10*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="42">
         <f>ENTRADAS!$B$6+A10*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="42">
         <f>B10-C10</f>
         <v/>
       </c>
@@ -2533,18 +3154,18 @@
       <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="n">
+      <c r="A11" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="42">
         <f>A11*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="42">
         <f>ENTRADAS!$B$6+A11*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="42">
         <f>B11-C11</f>
         <v/>
       </c>
@@ -2554,18 +3175,18 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="n">
+      <c r="A12" s="23" t="n">
         <v>120</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="42">
         <f>A12*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="42">
         <f>ENTRADAS!$B$6+A12*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="42">
         <f>B12-C12</f>
         <v/>
       </c>
@@ -2575,18 +3196,18 @@
       <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="n">
+      <c r="A13" s="23" t="n">
         <v>140</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="42">
         <f>A13*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="42">
         <f>ENTRADAS!$B$6+A13*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="42">
         <f>B13-C13</f>
         <v/>
       </c>
@@ -2596,18 +3217,18 @@
       <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="n">
+      <c r="A14" s="23" t="n">
         <v>160</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="42">
         <f>A14*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="42">
         <f>ENTRADAS!$B$6+A14*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="42">
         <f>B14-C14</f>
         <v/>
       </c>
@@ -2617,18 +3238,18 @@
       <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="n">
+      <c r="A15" s="23" t="n">
         <v>180</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="42">
         <f>A15*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="42">
         <f>ENTRADAS!$B$6+A15*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="42">
         <f>B15-C15</f>
         <v/>
       </c>
@@ -2638,18 +3259,18 @@
       <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="n">
+      <c r="A16" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="42">
         <f>A16*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="42">
         <f>ENTRADAS!$B$6+A16*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="42">
         <f>B16-C16</f>
         <v/>
       </c>
@@ -2659,18 +3280,18 @@
       <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="23" t="n">
         <v>220</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="42">
         <f>A17*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="42">
         <f>ENTRADAS!$B$6+A17*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="42">
         <f>B17-C17</f>
         <v/>
       </c>
@@ -2680,18 +3301,18 @@
       <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="42">
         <f>A18*ENTRADAS!$B$9</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="42">
         <f>ENTRADAS!$B$6+A18*ENTRADAS!$B$8</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="42">
         <f>B18-C18</f>
         <v/>
       </c>
